--- a/diseases/d212/2020-2025.xlsx
+++ b/diseases/d212/2020-2025.xlsx
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12668,7 +12668,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13070,7 +13070,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13472,7 +13472,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14276,7 +14276,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14678,7 +14678,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15080,7 +15080,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15482,7 +15482,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15884,7 +15884,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16286,7 +16286,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17090,7 +17090,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17492,7 +17492,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17894,7 +17894,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18296,7 +18296,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18698,7 +18698,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19100,7 +19100,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19502,7 +19502,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19904,7 +19904,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20306,7 +20306,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20708,7 +20708,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21110,7 +21110,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21512,7 +21512,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21914,7 +21914,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22316,7 +22316,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22718,7 +22718,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23120,7 +23120,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23522,7 +23522,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23924,7 +23924,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24326,7 +24326,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24728,7 +24728,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -25130,7 +25130,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25532,7 +25532,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26336,7 +26336,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26738,7 +26738,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27542,7 +27542,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28346,7 +28346,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28748,7 +28748,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -29150,7 +29150,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29552,7 +29552,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29954,7 +29954,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30356,7 +30356,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30758,7 +30758,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -31160,7 +31160,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31562,7 +31562,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31964,7 +31964,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -32366,7 +32366,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32768,7 +32768,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -33170,7 +33170,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33572,7 +33572,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33974,7 +33974,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">

--- a/diseases/d212/2020-2025.xlsx
+++ b/diseases/d212/2020-2025.xlsx
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12668,7 +12668,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13070,7 +13070,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13472,7 +13472,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14276,7 +14276,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14678,7 +14678,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15080,7 +15080,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15482,7 +15482,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15884,7 +15884,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16286,7 +16286,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17090,7 +17090,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17492,7 +17492,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17894,7 +17894,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18296,7 +18296,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18698,7 +18698,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19100,7 +19100,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19502,7 +19502,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19904,7 +19904,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20306,7 +20306,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20708,7 +20708,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21110,7 +21110,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21512,7 +21512,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21914,7 +21914,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22316,7 +22316,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22718,7 +22718,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23120,7 +23120,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23522,7 +23522,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23924,7 +23924,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24326,7 +24326,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24728,7 +24728,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -25130,7 +25130,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25532,7 +25532,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26336,7 +26336,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26738,7 +26738,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27542,7 +27542,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28346,7 +28346,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28748,7 +28748,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -29150,7 +29150,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29552,7 +29552,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29954,7 +29954,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30356,7 +30356,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30758,7 +30758,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -31160,7 +31160,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31562,7 +31562,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31964,7 +31964,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -32366,7 +32366,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32768,7 +32768,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -33170,7 +33170,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33572,7 +33572,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33974,7 +33974,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">

--- a/diseases/d212/2020-2025.xlsx
+++ b/diseases/d212/2020-2025.xlsx
@@ -768,9 +768,6 @@
       <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -1170,9 +1167,6 @@
       <c r="P4" t="n">
         <v>3</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.0008734200758836097</v>
       </c>
@@ -1572,9 +1566,6 @@
       <c r="P6" t="n">
         <v>1</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -1974,9 +1965,6 @@
       <c r="P8" t="n">
         <v>1</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -2376,9 +2364,6 @@
       <c r="P10" t="n">
         <v>2</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.0005822800505890731</v>
       </c>
@@ -2778,9 +2763,6 @@
       <c r="P12" t="n">
         <v>3</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.0008684913819209351</v>
       </c>
@@ -3180,9 +3162,6 @@
       <c r="P14" t="n">
         <v>2</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.0005789942546139568</v>
       </c>
@@ -3582,9 +3561,6 @@
       <c r="P16" t="n">
         <v>2</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.0005789942546139568</v>
       </c>
@@ -3984,9 +3960,6 @@
       <c r="P18" t="n">
         <v>4</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.001157988509227914</v>
       </c>
@@ -4386,9 +4359,6 @@
       <c r="P20" t="n">
         <v>3</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.0008684913819209351</v>
       </c>
@@ -4788,9 +4758,6 @@
       <c r="P22" t="n">
         <v>1</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -5190,9 +5157,6 @@
       <c r="P24" t="n">
         <v>1</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -5592,9 +5556,6 @@
       <c r="P26" t="n">
         <v>2</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.0005789942546139568</v>
       </c>
@@ -5994,9 +5955,6 @@
       <c r="P28" t="n">
         <v>1</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -6396,9 +6354,6 @@
       <c r="P30" t="n">
         <v>5</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.001447485636534892</v>
       </c>
@@ -6798,9 +6753,6 @@
       <c r="P32" t="n">
         <v>5</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.001447485636534892</v>
       </c>
@@ -7200,9 +7152,6 @@
       <c r="P34" t="n">
         <v>3</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.0008684913819209351</v>
       </c>
@@ -7602,9 +7551,6 @@
       <c r="P36" t="n">
         <v>3</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.0008684913819209351</v>
       </c>
@@ -8004,9 +7950,6 @@
       <c r="P38" t="n">
         <v>3</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.0008684913819209351</v>
       </c>
@@ -8406,9 +8349,6 @@
       <c r="P40" t="n">
         <v>1</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -8808,9 +8748,6 @@
       <c r="P42" t="n">
         <v>1</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -9210,9 +9147,6 @@
       <c r="P44" t="n">
         <v>1</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -9612,9 +9546,6 @@
       <c r="P46" t="n">
         <v>3</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.0008684913819209351</v>
       </c>
@@ -10014,9 +9945,6 @@
       <c r="P48" t="n">
         <v>1</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -10416,9 +10344,6 @@
       <c r="P50" t="n">
         <v>2</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.0005789942546139568</v>
       </c>
@@ -10818,9 +10743,6 @@
       <c r="P52" t="n">
         <v>3</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.0008684913819209351</v>
       </c>
@@ -11220,9 +11142,6 @@
       <c r="P54" t="n">
         <v>2</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.0005789942546139568</v>
       </c>
@@ -11622,9 +11541,6 @@
       <c r="P56" t="n">
         <v>1</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -12024,9 +11940,6 @@
       <c r="P58" t="n">
         <v>1</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -12426,9 +12339,6 @@
       <c r="P60" t="n">
         <v>1</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -12828,9 +12738,6 @@
       <c r="P62" t="n">
         <v>2</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.0005789942546139568</v>
       </c>
@@ -13230,9 +13137,6 @@
       <c r="P64" t="n">
         <v>1</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -13632,9 +13536,6 @@
       <c r="P66" t="n">
         <v>2</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.0005789942546139568</v>
       </c>
@@ -14034,9 +13935,6 @@
       <c r="P68" t="n">
         <v>2</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.0005789942546139568</v>
       </c>
@@ -14436,9 +14334,6 @@
       <c r="P70" t="n">
         <v>2</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.0005789942546139568</v>
       </c>
@@ -14838,9 +14733,6 @@
       <c r="P72" t="n">
         <v>2</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.0005789942546139568</v>
       </c>
@@ -15240,9 +15132,6 @@
       <c r="P74" t="n">
         <v>1</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -15642,9 +15531,6 @@
       <c r="P76" t="n">
         <v>3</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.0008684913819209351</v>
       </c>
@@ -16044,9 +15930,6 @@
       <c r="P78" t="n">
         <v>1</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -16446,9 +16329,6 @@
       <c r="P80" t="n">
         <v>1</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -16848,9 +16728,6 @@
       <c r="P82" t="n">
         <v>1</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -17250,9 +17127,6 @@
       <c r="P84" t="n">
         <v>1</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -17652,9 +17526,6 @@
       <c r="P86" t="n">
         <v>5</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.001447485636534892</v>
       </c>
@@ -18054,9 +17925,6 @@
       <c r="P88" t="n">
         <v>1</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -18456,9 +18324,6 @@
       <c r="P90" t="n">
         <v>3</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.0008684913819209351</v>
       </c>
@@ -18858,9 +18723,6 @@
       <c r="P92" t="n">
         <v>1</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -19260,9 +19122,6 @@
       <c r="P94" t="n">
         <v>1</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -19662,9 +19521,6 @@
       <c r="P96" t="n">
         <v>1</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -20064,9 +19920,6 @@
       <c r="P98" t="n">
         <v>4</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.001157988509227914</v>
       </c>
@@ -20466,9 +20319,6 @@
       <c r="P100" t="n">
         <v>1</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.0002879555610852622</v>
       </c>
@@ -20868,9 +20718,6 @@
       <c r="P102" t="n">
         <v>2</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.0005759111221705244</v>
       </c>
@@ -21270,9 +21117,6 @@
       <c r="P104" t="n">
         <v>2</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.0005759111221705244</v>
       </c>
@@ -21672,9 +21516,6 @@
       <c r="P106" t="n">
         <v>1</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.0002879555610852622</v>
       </c>
@@ -22074,9 +21915,6 @@
       <c r="P108" t="n">
         <v>5</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.001439777805426311</v>
       </c>
@@ -22476,9 +22314,6 @@
       <c r="P110" t="n">
         <v>3</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.0008638666832557865</v>
       </c>
@@ -22878,9 +22713,6 @@
       <c r="P112" t="n">
         <v>1</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.0002879555610852622</v>
       </c>
@@ -23280,9 +23112,6 @@
       <c r="P114" t="n">
         <v>4</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.001151822244341049</v>
       </c>
@@ -23682,9 +23511,6 @@
       <c r="P116" t="n">
         <v>2</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.0005759111221705244</v>
       </c>
@@ -24084,9 +23910,6 @@
       <c r="P118" t="n">
         <v>1</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.0002879555610852622</v>
       </c>
@@ -24486,9 +24309,6 @@
       <c r="P120" t="n">
         <v>6</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.001727733366511573</v>
       </c>
@@ -24888,9 +24708,6 @@
       <c r="P122" t="n">
         <v>4</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.001151822244341049</v>
       </c>
@@ -25290,9 +25107,6 @@
       <c r="P124" t="n">
         <v>1</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.0002879555610852622</v>
       </c>
@@ -25692,9 +25506,6 @@
       <c r="P126" t="n">
         <v>2</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.0005759111221705244</v>
       </c>
@@ -26094,9 +25905,6 @@
       <c r="P128" t="n">
         <v>1</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.0002879555610852622</v>
       </c>
@@ -26496,9 +26304,6 @@
       <c r="P130" t="n">
         <v>3</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.0008638666832557865</v>
       </c>
@@ -26898,9 +26703,6 @@
       <c r="P132" t="n">
         <v>2</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.0005759111221705244</v>
       </c>
@@ -27300,9 +27102,6 @@
       <c r="P134" t="n">
         <v>1</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.0002879555610852622</v>
       </c>
@@ -27702,9 +27501,6 @@
       <c r="P136" t="n">
         <v>2</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.0005759111221705244</v>
       </c>
@@ -28104,9 +27900,6 @@
       <c r="P138" t="n">
         <v>2</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.0005759111221705244</v>
       </c>
@@ -28506,9 +28299,6 @@
       <c r="P140" t="n">
         <v>3</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.0008638666832557865</v>
       </c>
@@ -28908,9 +28698,6 @@
       <c r="P142" t="n">
         <v>2</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.0005759111221705244</v>
       </c>
@@ -29310,9 +29097,6 @@
       <c r="P144" t="n">
         <v>1</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0.0002879555610852622</v>
       </c>
@@ -29712,9 +29496,6 @@
       <c r="P146" t="n">
         <v>2</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.0005759111221705244</v>
       </c>
@@ -30114,9 +29895,6 @@
       <c r="P148" t="n">
         <v>1</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.0002879555610852622</v>
       </c>
@@ -30516,9 +30294,6 @@
       <c r="P150" t="n">
         <v>4</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.001151822244341049</v>
       </c>
@@ -30918,9 +30693,6 @@
       <c r="P152" t="n">
         <v>3</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0.0008638666832557865</v>
       </c>
@@ -31320,9 +31092,6 @@
       <c r="P154" t="n">
         <v>2</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0.0005759111221705244</v>
       </c>
@@ -31722,9 +31491,6 @@
       <c r="P156" t="n">
         <v>1</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0.0002879555610852622</v>
       </c>
@@ -32124,9 +31890,6 @@
       <c r="P158" t="n">
         <v>3</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0.0008638666832557865</v>
       </c>
@@ -32526,9 +32289,6 @@
       <c r="P160" t="n">
         <v>1</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.0002879555610852622</v>
       </c>
@@ -32928,9 +32688,6 @@
       <c r="P162" t="n">
         <v>1</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0.0002879555610852622</v>
       </c>
@@ -33330,9 +33087,6 @@
       <c r="P164" t="n">
         <v>2</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0.0005759111221705244</v>
       </c>
@@ -33731,9 +33485,6 @@
       </c>
       <c r="P166" t="n">
         <v>1</v>
-      </c>
-      <c r="Q166" t="n">
-        <v>0</v>
       </c>
       <c r="R166" t="n">
         <v>0.0002879555610852622</v>

--- a/diseases/d212/2020-2025.xlsx
+++ b/diseases/d212/2020-2025.xlsx
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10982,7 +10982,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11780,7 +11780,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12977,7 +12977,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13376,7 +13376,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13775,7 +13775,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14573,7 +14573,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14972,7 +14972,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15371,7 +15371,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15770,7 +15770,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16169,7 +16169,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16568,7 +16568,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16967,7 +16967,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17366,7 +17366,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17765,7 +17765,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18164,7 +18164,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18563,7 +18563,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18962,7 +18962,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19361,7 +19361,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19760,7 +19760,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20159,7 +20159,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20558,7 +20558,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20957,7 +20957,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21356,7 +21356,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21755,7 +21755,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22553,7 +22553,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22952,7 +22952,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23351,7 +23351,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23750,7 +23750,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24149,7 +24149,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24548,7 +24548,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24947,7 +24947,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25346,7 +25346,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25745,7 +25745,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26144,7 +26144,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26543,7 +26543,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26942,7 +26942,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27341,7 +27341,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27740,7 +27740,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28139,7 +28139,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28538,7 +28538,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28937,7 +28937,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29336,7 +29336,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29735,7 +29735,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30533,7 +30533,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30932,7 +30932,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31331,7 +31331,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31730,7 +31730,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -32129,7 +32129,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32528,7 +32528,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -32927,7 +32927,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33326,7 +33326,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33725,7 +33725,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">

--- a/diseases/d212/2020-2025.xlsx
+++ b/diseases/d212/2020-2025.xlsx
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10982,7 +10982,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11780,7 +11780,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12977,7 +12977,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13376,7 +13376,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13775,7 +13775,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14573,7 +14573,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14972,7 +14972,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15371,7 +15371,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15770,7 +15770,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16169,7 +16169,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16568,7 +16568,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16967,7 +16967,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17366,7 +17366,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17765,7 +17765,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18164,7 +18164,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18563,7 +18563,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18962,7 +18962,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19361,7 +19361,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19760,7 +19760,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20159,7 +20159,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20558,7 +20558,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20957,7 +20957,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21356,7 +21356,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21755,7 +21755,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22553,7 +22553,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22952,7 +22952,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23351,7 +23351,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23750,7 +23750,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24149,7 +24149,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24548,7 +24548,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24947,7 +24947,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25346,7 +25346,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25745,7 +25745,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26144,7 +26144,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26543,7 +26543,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26942,7 +26942,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27341,7 +27341,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27740,7 +27740,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28139,7 +28139,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28538,7 +28538,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28937,7 +28937,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29336,7 +29336,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29735,7 +29735,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30533,7 +30533,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30932,7 +30932,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31331,7 +31331,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31730,7 +31730,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -32129,7 +32129,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32528,7 +32528,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -32927,7 +32927,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33326,7 +33326,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33725,7 +33725,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">

--- a/diseases/d212/2020-2025.xlsx
+++ b/diseases/d212/2020-2025.xlsx
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10982,7 +10982,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11780,7 +11780,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12977,7 +12977,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13376,7 +13376,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13775,7 +13775,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14573,7 +14573,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14972,7 +14972,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15371,7 +15371,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15770,7 +15770,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16169,7 +16169,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16568,7 +16568,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16967,7 +16967,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17366,7 +17366,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17765,7 +17765,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18164,7 +18164,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18563,7 +18563,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18962,7 +18962,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19361,7 +19361,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19760,7 +19760,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20159,7 +20159,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20558,7 +20558,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20957,7 +20957,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21356,7 +21356,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21755,7 +21755,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22553,7 +22553,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22952,7 +22952,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23351,7 +23351,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23750,7 +23750,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24149,7 +24149,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24548,7 +24548,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24947,7 +24947,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25346,7 +25346,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25745,7 +25745,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26144,7 +26144,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26543,7 +26543,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26942,7 +26942,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27341,7 +27341,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27740,7 +27740,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28139,7 +28139,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28538,7 +28538,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28937,7 +28937,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29336,7 +29336,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29735,7 +29735,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30533,7 +30533,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30932,7 +30932,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31331,7 +31331,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31730,7 +31730,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -32129,7 +32129,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32528,7 +32528,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -32927,7 +32927,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33326,7 +33326,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33725,7 +33725,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">

--- a/diseases/d212/2020-2025.xlsx
+++ b/diseases/d212/2020-2025.xlsx
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10982,7 +10982,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11780,7 +11780,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12977,7 +12977,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13376,7 +13376,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13775,7 +13775,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14573,7 +14573,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14972,7 +14972,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15371,7 +15371,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15770,7 +15770,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16169,7 +16169,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16568,7 +16568,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16967,7 +16967,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17366,7 +17366,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17765,7 +17765,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18164,7 +18164,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18563,7 +18563,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18962,7 +18962,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19361,7 +19361,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19760,7 +19760,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20159,7 +20159,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20558,7 +20558,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20957,7 +20957,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21356,7 +21356,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21755,7 +21755,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22553,7 +22553,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22952,7 +22952,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23351,7 +23351,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23750,7 +23750,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24149,7 +24149,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24548,7 +24548,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24947,7 +24947,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25346,7 +25346,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25745,7 +25745,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26144,7 +26144,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26543,7 +26543,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26942,7 +26942,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27341,7 +27341,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27740,7 +27740,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28139,7 +28139,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28538,7 +28538,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28937,7 +28937,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29336,7 +29336,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29735,7 +29735,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30533,7 +30533,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30932,7 +30932,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31331,7 +31331,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31730,7 +31730,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -32129,7 +32129,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32528,7 +32528,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -32927,7 +32927,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33326,7 +33326,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33725,7 +33725,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
